--- a/www/download/COUNTRY.FRA.rpPE.xlsx
+++ b/www/download/COUNTRY.FRA.rpPE.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>França</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>0.760282826729216</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.779672363475178</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>0.88864406087171</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.89809338282399</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>0.938262381425976</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>1.08271976661779</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>1.11656987383435</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>1.05752963960776</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.884017005403936</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>0.803923182788067</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.803793923948273</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>0.796431999963391</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>0.729660724914413</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902077640803</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948697621517</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22.694</t>
+          <t>-0.482346523306865</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>-0.470497576336099</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.879</t>
+          <t>-0.391493124122983</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.227</t>
+          <t>-0.394491717040667</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>23.696</t>
+          <t>-0.344845696565318</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>24.332</t>
+          <t>-0.277901737692456</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>24.765</t>
+          <t>-0.293117315336706</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.919</t>
+          <t>-0.346158117769605</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>-0.399093805320748</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24.977</t>
+          <t>-0.445463715842098</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>25.115</t>
+          <t>-0.427138306494265</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>25.362</t>
+          <t>-0.422003313535039</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>25.729</t>
+          <t>-0.426522297593097</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>25.945</t>
+          <t>-0.44019055944294</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>25.522</t>
+          <t>-0.43671466355661</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20.264</t>
+          <t>-0.605676330007156</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20.419</t>
+          <t>-0.598138401807012</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20.574</t>
+          <t>-0.56713839448844</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.968</t>
+          <t>-0.574079317800831</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>21.455</t>
+          <t>-0.548464861313305</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>22.102</t>
+          <t>-0.504205181703523</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22.56</t>
+          <t>-0.512465064327759</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22.725</t>
+          <t>-0.559820904668872</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>22.759</t>
+          <t>-0.614803501506074</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>22.768</t>
+          <t>-0.640536643043513</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>22.875</t>
+          <t>-0.633351016818127</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>23.097</t>
+          <t>-0.638701948515621</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>23.444</t>
+          <t>-0.633102170437416</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>-0.636386497960159</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>23.244</t>
+          <t>-0.636554654359016</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>35398.487</t>
+          <t>-0.854563080311838</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>35593.522</t>
+          <t>-0.846841511605418</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35567.12</t>
+          <t>-0.83634621397238</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>35886.025</t>
+          <t>-0.847887572620577</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>36560.307</t>
+          <t>-0.843594290780453</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>36624.674</t>
+          <t>-0.83549116828645</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>37045.329</t>
+          <t>-0.839668184621465</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>36392.365</t>
+          <t>-0.854840108173027</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>36304.468</t>
+          <t>-0.887114785149031</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>36998.921</t>
+          <t>-0.875513447157127</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>37190.257</t>
+          <t>-0.870976197226915</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>37129.413</t>
+          <t>-0.869159052918385</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>38094.743</t>
+          <t>-0.856315252268178</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>38629.06</t>
+          <t>-0.853039654067038</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>37490.919</t>
+          <t>-0.854671159801651</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>31468.573</t>
+          <t>161045555404.017</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>31797.298</t>
+          <t>157786713971.238</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31910.139</t>
+          <t>148693646827.089</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>32356.773</t>
+          <t>162823573231.159</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>33060.697</t>
+          <t>177784082745.174</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>33182.202</t>
+          <t>191195046064.632</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>33644.776</t>
+          <t>191593948384.658</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>33067.66</t>
+          <t>185011027980.159</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>33001.137</t>
+          <t>174948927639.204</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>33623.177</t>
+          <t>190013056789.333</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>33760.725</t>
+          <t>190153476054.732</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>33683.49</t>
+          <t>188956061735.101</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>34563.816</t>
+          <t>183975869935.862</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>34927.705</t>
+          <t>166667045047.437</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>34397.205</t>
+          <t>151976513313.475</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>280259432582.105</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>274143040175.552</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>253719971736.188</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>29.46</t>
+          <t>276482861311.547</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>274274556093.711</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>262329560980.797</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>273614491204.499</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>293103493735.914</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>313151991095.036</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>343968075239.964</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>32.68</t>
+          <t>331483965447.249</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>323843968106.896</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>309390846291.93</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>35.36</t>
+          <t>305244938732.233</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>37.49</t>
+          <t>305741127176.241</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>2653694.5485824</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>40.83</t>
+          <t>2635343.19606804</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>2733444.64417253</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>2897286.97715092</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>3125469.18793023</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>3566265.28848225</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>3572156.95843554</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>3306958.85226037</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>2599933.69509059</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>2484461.13335932</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>2374039.5495675</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>2207621.79449968</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>43.83</t>
+          <t>1853663.20095066</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>1494755.3491197</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>42.37</t>
+          <t>1480199.08158287</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>230958.265091265</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>233255.428203083</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>231648.977282782</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>234900.836153188</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>248313.431496289</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>249518.312866072</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>243258.650064106</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>242351.942555105</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>253687.293771689</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24.18</t>
+          <t>281185.307375659</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>301556.329997097</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>315020.532153848</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>364696.812103465</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>403532.051258606</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>368499.723684023</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>531357.754291017</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>526642.411422926</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>485556.646167748</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>43.19</t>
+          <t>504440.677890762</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>557611.272168147</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>583418.333269595</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>46.23</t>
+          <t>563953.958415469</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>559118.923447987</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>612967.95273469</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>691587.851522288</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>749892.676153509</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>792370.613926859</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>911915.841766077</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>50.76</t>
+          <t>938666.825931579</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>53.35</t>
+          <t>788453.407632309</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>47.31</t>
+          <t>-0.631630385299524</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.39</t>
+          <t>-0.61816418653234</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>-0.573686216957704</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>-0.575968077362235</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>-0.541667562445844</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>45.18</t>
+          <t>-0.49142222567282</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>44.94</t>
+          <t>-0.497496339632317</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>-0.539353341531115</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>-0.606842822086784</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>-0.614321779359302</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>-0.600343120012783</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>-0.598372577087575</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>-0.590160185361207</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>-0.59323727546102</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>39.21</t>
+          <t>-0.586856599773236</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>368936.495761504</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>374764.48329163</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>335780.252283257</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>341390.915017351</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>336675.801301864</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>304371.927123232</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>304156.833678665</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>325909.107965684</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>391806.062005809</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>446675.660307622</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>467880.918878405</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>495782.294355566</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>568435.887594481</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.760282826729216</t>
+          <t>13830.6149707164</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.779672363475178</t>
+          <t>13425.6825736216</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.88864406087171</t>
+          <t>12331.8884110851</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.89809338282399</t>
+          <t>13186.1949537165</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262381425976</t>
+          <t>12783.4743744563</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271976661779</t>
+          <t>11868.9343586067</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656987383435</t>
+          <t>12128.3556755348</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752963960776</t>
+          <t>12897.9570221042</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017005403936</t>
+          <t>13759.358461415</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923182788067</t>
+          <t>15107.2572178969</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793923948273</t>
+          <t>14491.2290139039</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431999963391</t>
+          <t>14021.1617240006</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660724914413</t>
+          <t>13197.0161359806</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902077640803</t>
+          <t>12945.0230801495</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948697621517</t>
+          <t>13153.3249256663</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>69205154302.1166</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>66128390993.7367</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>59715365861.2717</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>71734734222.3068</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>78048186716.2505</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>78784519935.1592</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>85956958704.8789</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>91331490595.3634</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>93438807173.9539</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>101167163250.779</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>95676030239.2852</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.176</t>
+          <t>90041685010.4388</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>84958651573.0845</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.486</t>
+          <t>83198542341.2801</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.408</t>
+          <t>74109763499.0656</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>69678812158.7082</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>67109224323.321</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>59404467169.9369</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>72272053086.0998</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>79411387718.5415</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>79962270161.7896</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>87713590016.8034</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>92366346369.6318</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.022</t>
+          <t>95417412795.9308</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.164</t>
+          <t>104539006440.96</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.208</t>
+          <t>97189200024.3012</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>92884336807.7559</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>88451962943.3961</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.607</t>
+          <t>86620059195.3399</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.522</t>
+          <t>77824293871.8728</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.606</t>
+          <t>-473657856.591652</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6.597</t>
+          <t>-980833329.58427</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5.931</t>
+          <t>310898691.334774</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5.983</t>
+          <t>-537318863.792998</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5.843</t>
+          <t>-1363201002.29106</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5.252</t>
+          <t>-1177750226.6304</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5.273</t>
+          <t>-1756631311.92454</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5.791</t>
+          <t>-1034855774.26843</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7.146</t>
+          <t>-1978605621.97694</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8.308</t>
+          <t>-3371843190.18036</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>8.753</t>
+          <t>-1513169785.01594</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9.475</t>
+          <t>-2842651797.3171</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>10.893</t>
+          <t>-3493311370.31159</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3421516854.05981</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3714530372.80723</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.756</t>
+          <t>5094.77830783342</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>5126.40642685739</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.477</t>
+          <t>5257.25400058513</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5591.36759850082</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.562</t>
+          <t>5859.08097045567</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.415</t>
+          <t>6036.27621973558</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.445</t>
+          <t>6094.54312119742</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>5941.4008033076</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.218</t>
+          <t>5409.59054258624</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3.699</t>
+          <t>5826.54008255982</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3.873</t>
+          <t>5791.51937487707</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4.126</t>
+          <t>5631.28304944868</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>4.729</t>
+          <t>5408.66264695547</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>5.238</t>
+          <t>5265.55285730159</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4.763</t>
+          <t>5434.20938407724</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>6221.74432181177</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>6219.25644344952</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>6367.29229047009</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.314</t>
+          <t>6801.8066132829</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>7117.68235658688</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.192</t>
+          <t>7347.84763028341</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.204</t>
+          <t>7374.81058667687</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>7136.14894736478</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.623</t>
+          <t>6451.93375285558</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>6933.31369778665</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.926</t>
+          <t>6878.95380506617</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.027</t>
+          <t>6701.84023800227</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2.328</t>
+          <t>6407.9233152731</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.575</t>
+          <t>6202.96865149767</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.401</t>
+          <t>6286.21802039661</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-48.23</t>
+          <t>334641.952358483</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-47.05</t>
+          <t>339102.429593058</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-39.15</t>
+          <t>338361.947319309</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-39.45</t>
+          <t>356010.326054089</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>351545.148073966</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-27.79</t>
+          <t>349817.317809759</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-29.31</t>
+          <t>348539.985685791</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-34.62</t>
+          <t>366869.085207075</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-39.91</t>
+          <t>427267.374881465</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>492932.356022327</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-42.71</t>
+          <t>517609.757116401</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-42.2</t>
+          <t>559843.131018762</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-42.65</t>
+          <t>636358.964634236</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-44.02</t>
+          <t>704818.857878209</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-43.67</t>
+          <t>564578.924978241</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-60.57</t>
+          <t>29776061775.7471</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-59.81</t>
+          <t>30434820695.4249</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-56.71</t>
+          <t>30732282363.6283</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-57.41</t>
+          <t>34488227179.2546</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-54.85</t>
+          <t>35381987993.9153</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-50.42</t>
+          <t>40237136378.0438</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-51.25</t>
+          <t>40136147329.2546</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-55.98</t>
+          <t>39056988133.0085</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-61.48</t>
+          <t>36804166080.9246</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-64.05</t>
+          <t>40601103707.6878</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-63.34</t>
+          <t>40954866348.1206</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-63.87</t>
+          <t>41914332926.9701</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-63.31</t>
+          <t>40590590137.45</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-63.64</t>
+          <t>38127781067.024</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-63.66</t>
+          <t>29430605394.5275</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-85.46</t>
+          <t>302123.13999991</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-84.68</t>
+          <t>302975.841954017</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-83.63</t>
+          <t>287321.781771823</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-84.79</t>
+          <t>308308.410831377</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-84.36</t>
+          <t>312844.666091991</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-83.55</t>
+          <t>329007.361220354</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-83.97</t>
+          <t>326535.268935928</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-85.48</t>
+          <t>338917.454608216</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-88.71</t>
+          <t>402447.844448814</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-87.55</t>
+          <t>476344.714126205</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-87.1</t>
+          <t>517951.353992813</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-86.92</t>
+          <t>569438.353670302</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-85.63</t>
+          <t>660250.998735164</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-85.3</t>
+          <t>745498.918639478</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-85.47</t>
+          <t>595525.523941251</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>141196.888</t>
+          <t>86444959049.7166</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>141672.796</t>
+          <t>83114336838.9392</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>145679.827</t>
+          <t>72699108143.7571</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>157986.923</t>
+          <t>87795545742.5546</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>168664.16</t>
+          <t>97569709064.4813</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>178787.094</t>
+          <t>110008693162.35</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>182633.497</t>
+          <t>116004819903.522</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>177824.268</t>
+          <t>117781432597.972</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>160977.038</t>
+          <t>120495029423.793</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>173173.376</t>
+          <t>135458965247.758</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>172766.989</t>
+          <t>136749530062.387</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>169972.742</t>
+          <t>134950947363.415</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>164872.022</t>
+          <t>131813033377.163</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>160935.295</t>
+          <t>130595644015.801</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>160438.503</t>
+          <t>111435003516.492</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>103239.059</t>
+          <t>32518.8123585726</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>104677.631</t>
+          <t>36126.5876390414</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>108164.321</t>
+          <t>51040.1655474852</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>117237.559</t>
+          <t>47701.9152227113</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>125708.926</t>
+          <t>38700.4819819742</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>133414.984</t>
+          <t>20809.956589405</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>137492.283</t>
+          <t>22004.7167498631</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>135017.145</t>
+          <t>27951.6305988591</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>123117.953</t>
+          <t>24819.5304326515</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>132660.995</t>
+          <t>16587.6418961222</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>132479.847</t>
+          <t>-341.596876412301</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>130064.618</t>
+          <t>-9595.22265153983</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>126800.687</t>
+          <t>-23892.0341009281</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>124162.263</t>
+          <t>-40680.0607612691</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>126314.929</t>
+          <t>-30946.5989630097</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>161045.555</t>
+          <t>-56668897273.9695</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>157786.714</t>
+          <t>-52679516143.5143</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>148693.647</t>
+          <t>-41966825780.1288</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>162823.573</t>
+          <t>-53307318563.3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>177784.083</t>
+          <t>-62187721070.5659</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>191195.046</t>
+          <t>-69771556784.3067</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>191593.948</t>
+          <t>-75868672574.267</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>185011.028</t>
+          <t>-78724444464.9638</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>174948.928</t>
+          <t>-83690863342.8686</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>190013.057</t>
+          <t>-94857861540.0702</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>190153.476</t>
+          <t>-95794663714.2661</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>188956.062</t>
+          <t>-93036614436.4445</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>183975.87</t>
+          <t>-91222443239.713</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>166667.045</t>
+          <t>-92467862948.7769</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>151976.513</t>
+          <t>-82004398121.9646</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>611707.97021</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.527</t>
+          <t>602083.05757</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>541075.1991</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>557301.82177</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>548213.37883</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>493853.54953</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>495516.68763</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>536888.96766</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>651243.12978</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>739343.0277</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>762241.7374</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>792088.88628</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>913676.90683</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.939</t>
+          <t>1003335.30351</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>913841.85861</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>69999.547</t>
+          <t>0.0214874980478178</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>69885.385</t>
+          <t>0.0203946882629584</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>70938.646</t>
+          <t>0.0226994586132939</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>75821.39</t>
+          <t>0.0257024505447698</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>79170.164</t>
+          <t>0.0248958017612591</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>81770.94</t>
+          <t>0.0269904100510636</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>82643.068</t>
+          <t>0.0275674707148418</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>80193.641</t>
+          <t>0.0278214639716462</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>72405.612</t>
+          <t>0.0292535607529896</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>77255.376</t>
+          <t>0.0292217635208822</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>76466.921</t>
+          <t>0.0285103754112603</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>75122.724</t>
+          <t>0.0272658790125107</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>73576.322</t>
+          <t>0.0288570212072069</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>71650.018</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>71029.312</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>814431.400719446</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>816271.905844365</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>734763.548543567</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>754329.977991125</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>755497.618081448</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>690557.264864149</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>699934.70624591</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>769508.450167643</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>947369.787305278</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>1078060.71345106</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>1117592.42423547</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>1176401.75190837</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>1335242.48594087</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>1485590.23912755</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>1407887.81680612</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>280259.433</t>
+          <t>894246.998996653</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>274143.04</t>
+          <t>892705.01409536</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>253719.972</t>
+          <t>801013.038454619</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>276482.861</t>
+          <t>819008.805657723</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>274274.556</t>
+          <t>818120.744067147</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>262329.561</t>
+          <t>745992.56218311</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>273614.491</t>
+          <t>754751.47190718</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>293103.494</t>
+          <t>829814.613127679</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>313151.991</t>
+          <t>1022196.98339448</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>343968.075</t>
+          <t>1164259.26328522</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>331483.965</t>
+          <t>1208123.46570889</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>323843.968</t>
+          <t>1272830.95291963</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>309390.846</t>
+          <t>1444932.84207016</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>305244.939</t>
+          <t>1607162.91533441</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>305741.127</t>
+          <t>1522197.41274275</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-63.16</t>
+          <t>6606237.27834427</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-61.82</t>
+          <t>6597440.64278686</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-57.37</t>
+          <t>5931238.33417218</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-57.6</t>
+          <t>5983081.67530815</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-54.17</t>
+          <t>5842802.91696989</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-49.14</t>
+          <t>5252449.91704269</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-49.75</t>
+          <t>5273150.96433174</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-53.94</t>
+          <t>5790693.10374269</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-60.68</t>
+          <t>7146351.84054792</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-61.43</t>
+          <t>8307578.21901045</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-60.03</t>
+          <t>8753350.30678464</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-59.84</t>
+          <t>9475332.64547453</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-59.02</t>
+          <t>10892653.4373844</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-59.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-58.69</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.654</t>
+          <t>894246.998996653</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.635</t>
+          <t>905746.400376988</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>918801.832632203</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.897</t>
+          <t>940052.459437422</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3.125</t>
+          <t>981622.468584074</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.566</t>
+          <t>1013261.46903243</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.572</t>
+          <t>1032226.7139286</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.307</t>
+          <t>1057654.65005924</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1073070.14098764</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.484</t>
+          <t>1103202.71840136</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.374</t>
+          <t>1126888.96813901</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.208</t>
+          <t>1160360.1641389</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1187878.1231997</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1209573.11132662</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1198736.03069254</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>814431.400719446</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>827146.0153162</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>841812.729803576</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>864968.55688532</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>904793.59331058</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>936405.287981728</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>956795.543496221</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>979715.68502854</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>995397.987320742</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1020658.53804146</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1041840.65866083</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1071716.33593557</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1098999.10791019</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1118875.74505498</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1105441.67426647</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>510888.006383347</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>509317.22853464</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>470416.151375381</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>495170.775882277</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>482137.064452853</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>446137.70415689</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>449524.26846282</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>487014.667522321</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>600862.299735516</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>689437.746454777</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>717442.222231105</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>754135.567870367</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>882765.418839838</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>967531.233165592</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>879299.371237249</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>103239059196.444</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>104677630751.929</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>108164320984.239</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>117237559258.326</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>125708925853.514</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>133414984263.84</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>137492283359.902</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>135017144975.005</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>123117953076.829</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>132660995215.755</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>132479847396.438</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>130064618336.506</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>126800687095.224</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>124162262930.457</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>126314928870.756</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>141196887813.629</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>141672796004.847</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>145679827230.581</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>157986922568.045</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>168664159962.861</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>178787093755.293</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>182633496773.759</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>177824268389.593</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>160977037520.497</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>173173376229.617</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>172766988500.378</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>169972742300.237</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>164872022147.988</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>160935294771.481</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>160438503243.722</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>69999546965.1131</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>69885384719.9218</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>70938646371.741</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>75821390252.2184</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>79170163616.3521</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>81770939653.2675</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>82643067840.9537</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>80193640645.5389</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>72405612402.8048</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>77255376393.7468</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>76466921465.8622</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>75122724234.4216</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>73576321625.9399</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>71650017564.4913</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>71029312094.233</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>22694100</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>22779700</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>22879400</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>23227200</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>23696500</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>24331900</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>24764500</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>24918800</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>24950200</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>24977000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>25115300</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>25362100</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>25729400</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>25944882.8155248</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>25522261.9901433</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>20263700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>20419300</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>20574300</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>20967600</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>21455400</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>22102200</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>22559900</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>22724800</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>22759200</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>22768400</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>22874800</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>23096800</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>23444000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>23580100</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>23244398.5763359</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>35398486633.4996</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>35593522062.4628</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>35567119821.5873</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>35886025437.3558</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>36560307098.763</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>36624673723.8078</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>37045328742.0656</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>36392364963.501</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>36304467884.9718</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>36998920660.15</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>37190256522.7356</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>37129413142.017</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>38094742835.7833</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>38629060336.6229</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>37490919447.5879</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>31468572871.479</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>31797297552.2686</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>31910139313.0704</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>32356772876.0978</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>33060696770.3918</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>33182201967.4061</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>33644775867.4926</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>33067659896.5064</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>33001137358.75</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>33623177266.6708</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>33760724650.5758</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>33683489572.0406</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>34563815576.0508</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>34927704665.6024</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>34397205461.9189</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.273592376994599</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.288068054217246</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.284083159498723</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.29461248402429</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.301886888327069</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.311240681765325</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.315466126812984</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.314644803851782</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.284851592450394</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.315755940723873</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.32678508147576</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.336017316639415</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.345621407234593</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.353555129748233</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.374934894575985</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.413160058376902</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.408308998377964</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.416854454368195</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.417823808883355</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.422771084810526</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.423025368000451</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.42603043269786</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.434453621079153</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.420193041419233</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.442463877183327</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.440757438924035</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.434024045809127</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.438329512209324</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.439977971085183</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.423741093157066</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.313247564628499</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.30362294740479</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.299062386133083</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.287563707092355</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.275342026862405</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.265733950234225</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.258503440489157</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.250901575069065</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.294955366130374</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.2417801820928</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.232457479600205</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.229958637551458</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.216049080556083</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.206466899166584</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.20132401226695</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.394631843178548</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.406424273924636</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.417567272256657</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.43192215911312</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.446741941605926</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.454978153042338</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.462332387466295</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.466564029721984</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.465005840304817</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.476069977369524</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.490675819588453</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.505975952643866</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.504591322015029</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.507608267506588</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.53354962942949</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.47313368585565</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.463891315813491</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.460337011404009</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.458126687667002</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.452352411348916</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.451767929250298</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.449396131153625</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.44889471578271</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.446000614659444</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.44153272756888</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.430395584891182</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.414989185316598</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.416197351238902</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.41466285712297</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.39206096872691</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.132234470965802</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.129684410261872</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.122095716339334</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.109951153219878</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.100905647045158</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0932539177073643</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0882714813800801</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0845412544953061</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0889935450357389</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0823972950615956</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0789285955203655</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0790348620395362</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0792113267460693</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0777288753704419</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0743894018435994</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2756128.53911</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2730003.4097</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2476918.08085</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2560238.46343</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2562027.48929</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2414855.70244</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2444529.532</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2639684.87457</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>3217567.05325</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>3699465.40247</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>3873089.74045</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>4125988.15742</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>4729165.05439</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>5238127.73635</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>4763177.36481</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1405135.00538</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1402022.24263</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1271429.18983</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1314179.58154</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1300257.80852</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1192130.26634</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1204275.74037</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1316829.28065</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1623059.28313</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1853697.00974</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1925565.68794</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026966.52079</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2327698.26091</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2574694.1485</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2401496.78398</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>5022608.58954871</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>5086111.62977844</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>5146899.00500912</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>5219839.20163923</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>5307549.10278604</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>5406133.78864236</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5504472.44716318</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>5588962.34068851</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>5675679.49993622</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>5765538.23372411</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>5861141.60089492</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>5961456.63870653</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>6072128.97709865</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
